--- a/out/LSTM-mamba2_repeat_1_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.780723568071307</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.780723568071307</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.780723568071307</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.180723568071307</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-5.470734959421679e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.0235552892915402</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001967608209063765</v>
+        <v>0.04717365639325231</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.397488741953415</v>
+        <v>0.09100653982477747</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7956734365003348</v>
+        <v>0.2056931264248386</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1108359290918626</v>
+        <v>0.02799463081832791</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.6192789398147811</v>
+        <v>0.1705589847875484</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01366189549499358</v>
+        <v>0.005678873425097509</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.5355461212627322</v>
+        <v>0.153879958549737</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01726981518233335</v>
+        <v>0.004917092903700887</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5563928295758166</v>
+        <v>0.1580298336115703</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008360440168600068</v>
+        <v>0.002400960930096784</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5558115351109428</v>
+        <v>0.157910286646544</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00390352333144561</v>
+        <v>0.001143586999493277</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5552441911256514</v>
+        <v>0.1577932609992251</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001468190675293465</v>
+        <v>0.000473214064411936</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5542707717987965</v>
+        <v>0.1575953407944017</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001195266833674351</v>
+        <v>0.0003268187407112325</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5551911554399845</v>
+        <v>0.1577747739985299</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004579638036026382</v>
+        <v>0.0001335217100878401</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5549094495041766</v>
+        <v>0.1577146379686887</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000239141160696394</v>
+        <v>6.649436238847041e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.554929497162519</v>
+        <v>0.1577146294899893</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.860402472114634e-05</v>
+        <v>2.334266066831255e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5548466865244056</v>
+        <v>0.1576940673623667</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.325085097013677e-05</v>
+        <v>1.0461098056069e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5548544261495523</v>
+        <v>0.1576916152873959</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.841329617673363e-05</v>
+        <v>2.340732518447637e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5548482645615057</v>
+        <v>0.1576863834801766</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.798606215163064e-06</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5548410543415607</v>
+        <v>0.1576809284348937</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-8.188108520026933e-07</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5548335956090226</v>
+        <v>0.1576754228010664</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.414534976498284e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5548277738035191</v>
+        <v>0.1576702293063323</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.589420887334386e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5548219090075178</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.163506086714776e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576649015120096</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576649413674818</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576649812229541</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576649732518597</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576651326737488</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576653877487716</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576651406448432</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.157665100789371</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576651087604654</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576651406448432</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576652362979769</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.157665172529221</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576651326737488</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576651087604654</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576648616565373</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576647819455925</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576648297721592</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576649493385763</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.1576649333963874</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5543867204177825</v>
+        <v>0.1576649493385763</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5355818012010045</v>
+        <v>0.1576649333963874</v>
       </c>
     </row>
     <row r="86">
@@ -69303,21 +69303,21 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.001338723185834066</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6022315743577573</v>
+        <v>0.1576649891940486</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6022259018701622</v>
+        <v>0.1576649891940486</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6022202295362432</v>
+        <v>0.1576649891940486</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.1110146380421343</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7785431170164696</v>
+        <v>0.1576651406448432</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.1183405415159946</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9039007467058914</v>
+        <v>0.1576653558643938</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.04637091062014155</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8780338041852455</v>
+        <v>0.1576652681823547</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.0196947207270193</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8709322038253318</v>
+        <v>0.157665220355788</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0.01159288624878965</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8743708097175399</v>
+        <v>0.1576652681823547</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0.002450779798260231</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8676461452487649</v>
+        <v>0.157665084847182</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0.001295634390951821</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8677772559791009</v>
+        <v>0.1576650928182765</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0.0006817645961904605</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8678402711026959</v>
+        <v>0.157665100789371</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>0.0003564912758646719</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8678692573453042</v>
+        <v>0.1576651087604654</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>0.0001757456379323359</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8678630405013119</v>
+        <v>0.1576651087604654</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0.0001081029846825929</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8679029595751907</v>
+        <v>0.1576651486159377</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>6.986651042216729e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8679340949958421</v>
+        <v>0.1576652123846936</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>4.837223656459734e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8679608219545055</v>
+        <v>0.1576653239800159</v>
       </c>
     </row>
     <row r="102">
@@ -82023,7 +82023,7 @@
         <v>0</v>
       </c>
       <c r="IY102" t="n">
-        <v>2.489111348741595e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.867962563088851</v>
+        <v>0.1576653718065827</v>
       </c>
     </row>
     <row r="103">
@@ -82818,7 +82818,7 @@
         <v>0</v>
       </c>
       <c r="IY103" t="n">
-        <v>8.722982296345431e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8679546454936539</v>
+        <v>0.1576653319511104</v>
       </c>
     </row>
     <row r="104">
@@ -83613,7 +83613,7 @@
         <v>0</v>
       </c>
       <c r="IY104" t="n">
-        <v>5.717234262600073e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8679470404080338</v>
+        <v>0.1576652602112603</v>
       </c>
     </row>
     <row r="105">
@@ -84408,7 +84408,7 @@
         <v>0</v>
       </c>
       <c r="IY105" t="n">
-        <v>-1.139331851942735e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8679441800867135</v>
+        <v>0.1576653797776771</v>
       </c>
     </row>
     <row r="106">
@@ -85203,7 +85203,7 @@
         <v>0</v>
       </c>
       <c r="IY106" t="n">
-        <v>-3.921069821561071e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8679377404919024</v>
+        <v>0.157665220355788</v>
       </c>
     </row>
     <row r="107">
@@ -85998,21 +85998,21 @@
         <v>0</v>
       </c>
       <c r="IY107" t="n">
-        <v>-4.805759003354694e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8679315800729159</v>
+        <v>0.1576649891940486</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8679315800729159</v>
+        <v>0.1576649413674818</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8679315800729159</v>
+        <v>0.1576649732518597</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8679315800729159</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8673677952855721</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="112">
@@ -89973,21 +89973,21 @@
         <v>0</v>
       </c>
       <c r="IY112" t="n">
-        <v>-0.1116446943680493</v>
+        <v>0</v>
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7557231009175228</v>
+        <v>0.1576649573096708</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7551901824967677</v>
+        <v>0.1576648377432537</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6863192237612037</v>
+        <v>0.1576647978877814</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.09225372064223651</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.940644374187425</v>
+        <v>0.1576649413674818</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.1063124358247762</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.06062530630413</v>
+        <v>0.1576650768760876</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.04961600148483957</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.053253724136742</v>
+        <v>0.1576650609338987</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.02215264919041553</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.047799095320638</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.008863704294620587</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.043302257232872</v>
+        <v>0.157664997165143</v>
       </c>
     </row>
     <row r="120">
@@ -96333,21 +96333,21 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.003110632541268223</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.037484435333937</v>
+        <v>0.1576648935409151</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.037484435333937</v>
+        <v>0.157664773974498</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.036996187497287</v>
+        <v>0.1576648935409151</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.002208221737091309</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.106367543902957</v>
+        <v>0.1576649413674818</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.09988504746067681</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.239834158697923</v>
+        <v>0.1576650370206153</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.155450078001128</v>
+        <v>0.1576649174541985</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.03018432225774196</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.168843616591725</v>
+        <v>0.1576649254252929</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_1_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963827</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.180723568071307</v>
+        <v>0.9753533038203248</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.780723568071307</v>
+        <v>0.9753533038203248</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963826</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.180723568071307</v>
+        <v>0.9753533038203248</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963826</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.180723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.780723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-7.49535626315046e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.03227272079862901</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001967608209063765</v>
+        <v>0.06463178392730863</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.397488741953415</v>
+        <v>0.1246874153560523</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7956734365003348</v>
+        <v>0.2818162098474703</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1108359290918626</v>
+        <v>0.03835403891343336</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.6192789398147811</v>
+        <v>0.2336800477341195</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01366189549499358</v>
+        <v>0.007782526362317263</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.5355461212627322</v>
+        <v>0.2108300406954919</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01726981518233335</v>
+        <v>0.006738446263266714</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5563928295758166</v>
+        <v>0.2165173706165694</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008360440168600068</v>
+        <v>0.003291383479728179</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5558115351109428</v>
+        <v>0.216355436842975</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00390352333144561</v>
+        <v>0.001568544144157456</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5552441911256514</v>
+        <v>0.2161969636612202</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001468190675293465</v>
+        <v>0.0006502479089788692</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5542707717987965</v>
+        <v>0.2159276661131824</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001195266833674351</v>
+        <v>0.0004495145076253858</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5551911554399845</v>
+        <v>0.216175296711395</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004579638036026382</v>
+        <v>0.0001844203849573256</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5549094495041766</v>
+        <v>0.216094773858659</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000239141160696394</v>
+        <v>9.322122683275844e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.554929497162519</v>
+        <v>0.2160966224296857</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.860402472114634e-05</v>
+        <v>3.383994239731721e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5548466865244056</v>
+        <v>0.2160702965510914</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.325085097013677e-05</v>
+        <v>1.618743066942789e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5548544261495523</v>
+        <v>0.2160687881520577</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.841329617673363e-05</v>
+        <v>5.164091179389035e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5548482645615057</v>
+        <v>0.216063470254021</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.798606215163064e-06</v>
+        <v>-2.045694596194254e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5548410543415607</v>
+        <v>0.2160578533114223</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-8.188108520026933e-07</v>
+        <v>-2.694140733653212e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5548335956090226</v>
+        <v>0.2160521301547936</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.414534976498284e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5548277738035191</v>
+        <v>0.2160468888334928</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.589420887334386e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5548219090075178</v>
+        <v>0.2160416008946423</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.163506086714776e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160363290605913</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160363689160636</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160364087715358</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160364008004414</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160365602223305</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.216036464569197</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160368152973533</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.216036568193425</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160365283379527</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.216036464569197</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160365363090472</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.216036464569197</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.216036568193425</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160366638465586</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160366000778028</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160365602223305</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160365363090472</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.216036289205119</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160362094941742</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.216036257320741</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.216036376887158</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5548162273802911</v>
+        <v>0.2160363609449691</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5543867204177825</v>
+        <v>0.216036376887158</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5355818012010045</v>
+        <v>0.2160363609449691</v>
       </c>
     </row>
     <row r="86">
@@ -69303,21 +69303,21 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.001338723185834066</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6022315743577573</v>
+        <v>0.2160364167426303</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6022259018701622</v>
+        <v>0.2160364167426303</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6022202295362432</v>
+        <v>0.2160364167426303</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.1110146380421343</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963826</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7785431170164696</v>
+        <v>0.216036568193425</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.1183405415159946</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.1066584434275599</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9039007467058914</v>
+        <v>0.2160367834129755</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.04637091062014155</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8780338041852455</v>
+        <v>0.2160366957309365</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.0196947207270193</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8709322038253318</v>
+        <v>0.2160366479043697</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0.01159288624878965</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8743708097175399</v>
+        <v>0.2160366957309365</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0.002450779798260231</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8676461452487649</v>
+        <v>0.2160365123957638</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0.001295634390951821</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8677772559791009</v>
+        <v>0.2160365203668582</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0.0006817645961904605</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8678402711026959</v>
+        <v>0.2160365283379527</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>0.0003564912758646719</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8678692573453042</v>
+        <v>0.2160365363090472</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>0.0001757456379323359</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8678630405013119</v>
+        <v>0.2160365363090472</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0.0001081029846825929</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.023677129033441</v>
+        <v>0.5343474301963826</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8679029595751907</v>
+        <v>0.2160365761645194</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>6.986651042216729e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963826</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8679340949958421</v>
+        <v>0.2160366399332753</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>4.837223656459734e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8679608219545055</v>
+        <v>0.2160367515285977</v>
       </c>
     </row>
     <row r="102">
@@ -82023,7 +82023,7 @@
         <v>0</v>
       </c>
       <c r="IY102" t="n">
-        <v>2.489111348741595e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.867962563088851</v>
+        <v>0.2160367993551644</v>
       </c>
     </row>
     <row r="103">
@@ -82818,7 +82818,7 @@
         <v>0</v>
       </c>
       <c r="IY103" t="n">
-        <v>8.722982296345431e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963826</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8679546454936539</v>
+        <v>0.2160367594996921</v>
       </c>
     </row>
     <row r="104">
@@ -83613,7 +83613,7 @@
         <v>0</v>
       </c>
       <c r="IY104" t="n">
-        <v>5.717234262600073e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.1066584434275598</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8679470404080338</v>
+        <v>0.216036687759842</v>
       </c>
     </row>
     <row r="105">
@@ -84408,7 +84408,7 @@
         <v>0</v>
       </c>
       <c r="IY105" t="n">
-        <v>-1.139331851942735e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8679441800867135</v>
+        <v>0.2160368073262589</v>
       </c>
     </row>
     <row r="106">
@@ -85203,7 +85203,7 @@
         <v>0</v>
       </c>
       <c r="IY106" t="n">
-        <v>-3.921069821561071e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8679377404919024</v>
+        <v>0.2160366479043697</v>
       </c>
     </row>
     <row r="107">
@@ -85998,21 +85998,21 @@
         <v>0</v>
       </c>
       <c r="IY107" t="n">
-        <v>-4.805759003354694e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8679315800729159</v>
+        <v>0.2160364167426303</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8679315800729159</v>
+        <v>0.2160363689160636</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8679315800729159</v>
+        <v>0.2160364008004414</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.3066584434275599</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8679315800729159</v>
+        <v>0.216036464569197</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963826</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8673677952855721</v>
+        <v>0.216036464569197</v>
       </c>
     </row>
     <row r="112">
@@ -89973,21 +89973,21 @@
         <v>0</v>
       </c>
       <c r="IY112" t="n">
-        <v>-0.1116446943680493</v>
+        <v>0</v>
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7557231009175228</v>
+        <v>0.2160363848582525</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7551901824967677</v>
+        <v>0.2160362652918354</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6863192237612037</v>
+        <v>0.2160362254363631</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.09225372064223651</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.940644374187425</v>
+        <v>0.2160363689160636</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.1063124358247762</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.06062530630413</v>
+        <v>0.2160365044246693</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.04961600148483957</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.053253724136742</v>
+        <v>0.2160364884824804</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.02215264919041553</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.047799095320638</v>
+        <v>0.216036464569197</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.008863704294620587</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963826</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.043302257232872</v>
+        <v>0.2160364247137248</v>
       </c>
     </row>
     <row r="120">
@@ -96333,21 +96333,21 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.003110632541268223</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.3066584434275598</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.037484435333937</v>
+        <v>0.2160363210894968</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.3066584434275598</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.037484435333937</v>
+        <v>0.2160362015230798</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963827</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.036996187497287</v>
+        <v>0.2160363210894968</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.002208221737091309</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.180723568071307</v>
+        <v>0.9753533038203248</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.106367543902957</v>
+        <v>0.2160363689160636</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.09988504746067681</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.239834158697923</v>
+        <v>0.216036464569197</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963828</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.155450078001128</v>
+        <v>0.2160363450027802</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.03018432225774196</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.2138444933844116</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.168843616591725</v>
+        <v>0.2160363529738747</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_1_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2754011154174805</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1494306623935699</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.04416364431381226</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.00529073178768158</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01383259147405624</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.175353303820325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001723064109683037</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01561766862869263</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.02016410604119301</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01407884806394577</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01930456981062889</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.175353303820325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01267293468117714</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.175353303820325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01498986408114433</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01079945638775826</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3343474301963827</v>
+        <v>-0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0006608553230762482</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>6.021745502948761e-05</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001656388863921165</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9753533038203248</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01522499322891235</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9753533038203248</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01518436148762703</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.175353303820325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01400108635425568</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01645742356777191</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.175353303820325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01535945013165474</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.175353303820325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0077357217669487</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5343474301963826</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.002948660403490067</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.002707783132791519</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004969125613570213</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.00930178165435791</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.9753533038203248</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.008828205987811089</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.175353303820325</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01513391733169556</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.007613698020577431</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5343474301963826</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.01257668994367123</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5343474301963825</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.006650406867265701</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.003240788355469704</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01681936532258987</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01644812896847725</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01908187940716743</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.175353303820325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01237283647060394</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.00899307057261467</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.175353303820325</v>
+        <v>0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.00910414382815361</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0002698563039302826</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.01123541966080666</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.003366454504430294</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.006618741899728775</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-7.49535626315046e-05</v>
+        <v>-2.975905342493206e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03227272079862901</v>
+        <v>0.01281327730767792</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.005970720201730728</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06463178392730863</v>
+        <v>0.02566096483563806</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1246874153560523</v>
+        <v>0.04950529396035906</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.01614228263497353</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2818162098474703</v>
+        <v>0.1118908286762438</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03835403891343336</v>
+        <v>0.01522759692281715</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.1085637137293816</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2336800477341195</v>
+        <v>0.09277907819874584</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.007782526362317263</v>
+        <v>0.003086838631631702</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.1758683621883392</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2108300406954919</v>
+        <v>0.08370368467059662</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.006738446263266714</v>
+        <v>0.002672618539613283</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.2402617037296295</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2165173706165694</v>
+        <v>0.08595893670423399</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003291383479728179</v>
+        <v>0.001304033150794584</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.2380445301532745</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.216355436842975</v>
+        <v>0.08589162276396481</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001568544144157456</v>
+        <v>0.0006197404563852321</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.2193230092525482</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2161969636612202</v>
+        <v>0.08582568967481796</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0006502479089788692</v>
+        <v>0.0002549836648199931</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.1838183701038361</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2159276661131824</v>
+        <v>0.08571575663521513</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0004495145076253858</v>
+        <v>0.0001755711286661125</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.150926411151886</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.216175296711395</v>
+        <v>0.0858111226114151</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001844203849573256</v>
+        <v>7.038158176873161e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.1232584416866302</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.216094773858659</v>
+        <v>0.08577611835331517</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>9.322122683275844e-05</v>
+        <v>3.375395344421761e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.1084737107157707</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2160966224296857</v>
+        <v>0.08577383498870163</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.383994239731721e-05</v>
+        <v>1.022105850705674e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0997043177485466</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2160702965510914</v>
+        <v>0.08576033407009277</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.618743066942789e-05</v>
+        <v>3.589498920038333e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0863603875041008</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2160687881520577</v>
+        <v>0.085756749583998</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.164091179389035e-06</v>
+        <v>-1.047297874682042e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.06940148770809174</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.216063470254021</v>
+        <v>0.08575162108575948</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.045694596194254e-07</v>
+        <v>-2.868697537608634e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.05476054549217224</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2160578533114223</v>
+        <v>0.08574636105988361</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.04259759932756424</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2160521301547936</v>
+        <v>0.08574107179723191</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.173194643232597e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.03401251509785652</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2160468888334928</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0328960008919239</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2160416008946423</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.02232755720615387</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2160363290605913</v>
+        <v>0.08573574388812552</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01961921900510788</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2160363689160636</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01022344455122948</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2160364087715358</v>
+        <v>0.08573582359907007</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.00949515588581562</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2160364008004414</v>
+        <v>0.08573581562797562</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01131678372621536</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2160365602223305</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01405433937907219</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.216036464569197</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02285965532064438</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2160368152973533</v>
+        <v>0.08573623012488754</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02618672698736191</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.216036568193425</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.03415093943476677</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2160365283379527</v>
+        <v>0.08573594316548691</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.02905510738492012</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.216036464569197</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.02638554945588112</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2160365363090472</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.02567396685481071</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.216036464569197</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.04360627755522728</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.216036568193425</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.05091066285967827</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2160366638465586</v>
+        <v>0.08573607867409289</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.05212977528572083</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2160366000778028</v>
+        <v>0.08573601490533701</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.04765153303742409</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2160365602223305</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.05641325935721397</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2160365363090472</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.04979880899190903</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.216036289205119</v>
+        <v>0.08573570403265325</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.03127027675509453</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2160362094941742</v>
+        <v>0.08573562432170846</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01555582135915756</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.216036257320741</v>
+        <v>0.08573567214827518</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005034415051341057</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.216036376887158</v>
+        <v>0.08573579171469226</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.00409126840531826</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.10665844342756</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2160363609449691</v>
+        <v>0.08573577577250334</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.0001841895282268524</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.216036376887158</v>
+        <v>0.08573579171469226</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.004044413566589355</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2160363609449691</v>
+        <v>0.08573577577250334</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.006987381726503372</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2160364167426303</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01359311491250992</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2160364167426303</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0018434077501297</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.175353303820325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2160364167426303</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.008439702913165092</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5343474301963826</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.216036568193425</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.007196035236120224</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1066584434275599</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2160367834129755</v>
+        <v>0.08573619824050972</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004076912999153137</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2160366957309365</v>
+        <v>0.0857361105584707</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.001292997971177101</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2160366479043697</v>
+        <v>0.08573606273190398</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.009575136005878448</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2160366957309365</v>
+        <v>0.0857361105584707</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.005180742591619492</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2160365123957638</v>
+        <v>0.08573592722329799</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.001345245167613029</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2160365203668582</v>
+        <v>0.08573593519439246</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0002282615751028061</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.30665844342756</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2160365283379527</v>
+        <v>0.08573594316548691</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.007180420681834221</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3343474301963825</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2160365363090472</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0115132387727499</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2160365363090472</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.001681538298726082</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5343474301963826</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2160365761645194</v>
+        <v>0.08573599099205365</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.002169162034988403</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5343474301963826</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2160366399332753</v>
+        <v>0.08573605476080952</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.002529377117753029</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.175353303820325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2160367515285977</v>
+        <v>0.0857361663561319</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.004936987534165382</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.175353303820325</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2160367993551644</v>
+        <v>0.08573621418269864</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.0003534834831953049</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.5343474301963826</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2160367594996921</v>
+        <v>0.08573617432722636</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.001268684864044189</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1066584434275598</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.216036687759842</v>
+        <v>0.08573610258737625</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01059991866350174</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2160368073262589</v>
+        <v>0.08573622215379309</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02408049628138542</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2160366479043697</v>
+        <v>0.08573606273190398</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02203758805990219</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2160364167426303</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01499899849295616</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2160363689160636</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003719717264175415</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2160364008004414</v>
+        <v>0.08573581562797562</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003957668319344521</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3066584434275599</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.216036464569197</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.0007275473326444626</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.5343474301963826</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.216036464569197</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.001698879525065422</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2160363848582525</v>
+        <v>0.08573579968578671</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.001029586419463158</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.175353303820325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2160362652918354</v>
+        <v>0.08573568011936965</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.009071698412299156</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.175353303820325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2160362254363631</v>
+        <v>0.08573564026389736</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0102786011993885</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.175353303820325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2160363689160636</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.01503373682498932</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2160365044246693</v>
+        <v>0.08573591925220354</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01760488748550415</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.175353303820325</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2160364884824804</v>
+        <v>0.08573590331001463</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.01374118402600288</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.216036464569197</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.008743699640035629</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5343474301963826</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2160364247137248</v>
+        <v>0.08573583954125899</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.004841438494622707</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3066584434275598</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2160363210894968</v>
+        <v>0.08573573591703107</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.005296146497130394</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3066584434275598</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2160362015230798</v>
+        <v>0.085735616350614</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.005272544920444489</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.3343474301963827</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2160363210894968</v>
+        <v>0.08573573591703107</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.006629437208175659</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9753533038203248</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2160363689160636</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.007914287969470024</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.216036464569197</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.006323032081127167</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5343474301963828</v>
+        <v>-0.3700000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2160363450027802</v>
+        <v>0.08573575983031444</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002304574474692345</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2138444933844116</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2160363529738747</v>
+        <v>0.08573576780140889</v>
       </c>
     </row>
   </sheetData>
